--- a/data/trans_orig/IP31KM07_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM07_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67900</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70234</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69039</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72542</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>136939</t>
+          <t>109273</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127134</t>
+          <t>104228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141206</t>
+          <t>111896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6122</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89679</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75211</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97900</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76492</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30943</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>100119</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>97880</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84323</t>
+          <t>67878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108340</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>174372</t>
+          <t>166594</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118543</t>
+          <t>150735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>178382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17051</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39740</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>49157</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25530</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94706</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>77699</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51220</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133528</t>
+          <t>63549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53479</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49598</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55961</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>50276</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45933</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52879</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>49085</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>45126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>51795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>110623</t>
+          <t>102564</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105251</t>
+          <t>97496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114635</t>
+          <t>106399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2673</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9619</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51088</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59226</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>56912</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49846</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>61521</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100386</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122778</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18728</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10590</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28214</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12770</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8161</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19836</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>41501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38949</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36362</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40093</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37553</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>74319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46608</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>44293</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>42429</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>39018</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43749</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53162</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50547</t>
+          <t>38997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95591</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92265</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>90891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5272</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>115411</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>102288</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>82,1%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>114351</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>108294</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>118743</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>124694</t>
+          <t>112030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107140</t>
+          <t>106472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134707</t>
+          <t>116506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>239045</t>
+          <t>227442</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218187</t>
+          <t>212509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249918</t>
+          <t>236212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25160</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16407</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>38283</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>9345</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>4953</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15402</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>49885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>150751</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>143634</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>154043</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>124270</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>119592</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>127051</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141986</t>
+          <t>127596</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151242</t>
+          <t>135759</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>272152</t>
+          <t>283789</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>265234</t>
+          <t>275982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276830</t>
+          <t>288641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6385</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9073</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>582763</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>619772</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>87,85%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>830</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>566831</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>481405</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>596171</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>623159</t>
+          <t>544874</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>667911</t>
+          <t>570790</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1129051</t>
+          <t>1137367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1246222</t>
+          <t>1185217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>83472</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>86303</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>56963</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>171729</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>183066</t>
+          <t>142735</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>151645</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268816</t>
+          <t>167664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
